--- a/output/pdf_financials_xlsx/DAT.H.xlsx
+++ b/output/pdf_financials_xlsx/DAT.H.xlsx
@@ -5932,29 +5932,25 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.06594</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.06594</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.06594</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.06594</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0.06594</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>0.06594</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.06594</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>0</v>
@@ -10243,7 +10239,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11329,7 +11329,11 @@
           <t>Reserves 65,940</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -13088,7 +13092,11 @@
           <t>Reserves 65,940</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DAT.H.xlsx
+++ b/output/pdf_financials_xlsx/DAT.H.xlsx
@@ -1134,10 +1134,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.003244</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.008418999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2168,10 +2168,10 @@
         <v>-0.01678</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.017089</v>
+        <v>-0.020333</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.015909</v>
+        <v>-0.024328</v>
       </c>
     </row>
     <row r="28">
@@ -2300,10 +2300,10 @@
         <v>-0.01678</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.017089</v>
+        <v>-0.020333</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.015909</v>
+        <v>-0.024328</v>
       </c>
     </row>
     <row r="30">
@@ -2550,44 +2550,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.089853</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.200582</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.140825</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.018439</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000165</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>6.9e-05</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5e-06</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>7.499999999999999e-05</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0.000167</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.8e-05</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.267289</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0.249245</v>
@@ -2662,44 +2658,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.089853</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.200582</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.140825</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.018439</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000165</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>6.9e-05</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5e-06</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>7.499999999999999e-05</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0.000167</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.8e-05</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.267289</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0.249245</v>
@@ -3334,22 +3326,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.089853</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.201015</v>
+        <v>0.000433</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.140825</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.018439</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.000165</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -9679,7 +9671,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -10777,7 +10769,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11669,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -12148,7 +12140,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -12619,7 +12611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -13363,7 +13355,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -13929,7 +13921,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -14681,7 +14673,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -16064,7 +16056,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
@@ -26027,7 +26019,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -26391,11 +26383,7 @@
           <t>General and administrative fees</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -26486,7 +26474,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
